--- a/domain/demo_corpus/files/pci_compliance_checklist_2020.xlsx
+++ b/domain/demo_corpus/files/pci_compliance_checklist_2020.xlsx
@@ -472,7 +472,6 @@
           <t>FW config review Q1 2020</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -490,7 +489,6 @@
           <t>Legacy device found</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -508,7 +506,6 @@
           <t>Code review logs</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -526,7 +523,6 @@
           <t>IAM audit 2020-02</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
